--- a/samples/class_schedule_sample.xlsx
+++ b/samples/class_schedule_sample.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
